--- a/docs/StructureDefinition-RNDSProfissional.xlsx
+++ b/docs/StructureDefinition-RNDSProfissional.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8996" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8997" uniqueCount="919">
   <si>
     <t>Property</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -3104,7 +3104,9 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -4490,7 +4492,7 @@
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>76</v>
@@ -7452,7 +7454,7 @@
         <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>76</v>
@@ -10414,7 +10416,7 @@
         <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>76</v>
@@ -13376,7 +13378,7 @@
         <v>87</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>76</v>
@@ -16338,7 +16340,7 @@
         <v>87</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>76</v>
@@ -19300,7 +19302,7 @@
         <v>87</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>76</v>
@@ -22262,7 +22264,7 @@
         <v>87</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>76</v>
@@ -25224,7 +25226,7 @@
         <v>87</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-RNDSProfissional.xlsx
+++ b/docs/StructureDefinition-RNDSProfissional.xlsx
@@ -616,7 +616,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/namingsystem-identifier-system-type</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0203</t>
   </si>
   <si>
     <t>Identifier.type</t>
